--- a/output/2026-09-01_09_Italia_Emilia_Romagna_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-01_09_Italia_Emilia_Romagna_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -495,10 +495,9 @@
           <t>0536 071051</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Azienda reale, oltre 25 anni di attività, confermata da sito ufficiale e directory (123aziende, reteimprese). Email generica non reperita.</t>
+          <t>Azienda reale, oltre 25 anni di attività, confermata da sito ufficiale e directory (123aziende, reteimprese). Email generica non reperita. [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,11 +527,9 @@
           <t>Impianti aspirazione industriale, fumi saldatura, officine meccaniche</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Azienda reale confermata da pagine proprie del sito (30 anni di attività, referenze a Reggio Emilia). Telefono/email/indirizzo non reperiti.</t>
+          <t>Azienda reale confermata da pagine proprie del sito (30 anni di attività, referenze a Reggio Emilia). Telefono/email/indirizzo non reperiti. [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -574,7 +571,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Confermata attiva dal 1997, divisione aspirazione industriale dal 2007. L'email usa dominio fevi.it (sito gemello del gruppo) - da ricontrollare.</t>
+          <t>Confermata attiva dal 1997, divisione aspirazione industriale dal 2007. L'email usa dominio fevi.it (sito gemello del gruppo) - da ricontrollare. [DUPLICATO — vedi anche: 2026-08-31_20_Italia_Emilia_Romagna_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -616,7 +613,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Confermata pagina dedicata 'impianti di aspirazione industriale' sul sito ufficiale.</t>
+          <t>Confermata pagina dedicata 'impianti di aspirazione industriale' sul sito ufficiale. [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -651,10 +648,9 @@
           <t>0543 795959</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Confermata: oltre 25 anni di attività, 25.000+ installazioni. Email non reperita.</t>
+          <t>Confermata: oltre 25 anni di attività, 25.000+ installazioni. Email non reperita. [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -689,10 +685,9 @@
           <t>348 5709040 / 349 5687601</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Confermata esistenza tramite sito ufficiale. Email non reperita.</t>
+          <t>Confermata esistenza tramite sito ufficiale. Email non reperita. [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -722,11 +717,9 @@
           <t>Impianti aspirazione e filtrazione aria/fumi/polveri industriali, ATEX, cabine di aspirazione</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sede legale verificata in Via Balduina 7, 42010 Rio Saliceto (RE) tramite visura camerale (P.IVA 01436110355). Azienda storica (fine anni '70).</t>
+          <t>Sede legale verificata in Via Balduina 7, 42010 Rio Saliceto (RE) tramite visura camerale (P.IVA 01436110355). Azienda storica (fine anni '70). [DUPLICATO — vedi anche: 2026-08-31_17_Italia_Emilia_Romagna_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -756,11 +749,9 @@
           <t>Impianti di aspirazione su misura, filtri disoleatori, abbattimento polveri/fumi</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Confermata azienda familiare attiva dai primi anni '80. Fonti con indirizzi discordanti non attribuibili con certezza - telefono/email lasciati vuoti.</t>
+          <t>Confermata azienda familiare attiva dai primi anni '80. Fonti con indirizzi discordanti non attribuibili con certezza - telefono/email lasciati vuoti. [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -844,7 +835,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Confermata, opera in ER e Marche. Email su dominio .it mentre sito è .net - verosimilmente stessa azienda, da ricontrollare.</t>
+          <t>Confermata, opera in ER e Marche. Email su dominio .it mentre sito è .net - verosimilmente stessa azienda, da ricontrollare. [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -916,8 +907,6 @@
           <t>Officina meccanica/carpenteria (attività primaria) + impianti abbattimento polveri e aspirazione fumi industriali (attività secondaria confermata dal sito)</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>Attività duale: prevalentemente carpenteria/officina, ma con sezioni dedicate ad abbattimento polveri/aspirazione fumi - da qualificare in fase commerciale.</t>
@@ -962,7 +951,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Azienda reale e consolidata (30+ anni) ma core business è pulizia industriale/aspirapolveri, non impiantistica fissa di aspirazione fumi saldatura - valutare pertinenza.</t>
+          <t>Azienda reale e consolidata (30+ anni) ma core business è pulizia industriale/aspirapolveri, non impiantistica fissa di aspirazione fumi saldatura - valutare pertinenza. [DUPLICATO — vedi anche: 2026-08-31_13_Italia_Toscana_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -997,7 +986,6 @@
           <t>035 4496693</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Azienda reale e consolidata (30+ anni, ISO 9001) ma sede legale in Lombardia. Includere solo se si accetta copertura commerciale extra-regionale.</t>
@@ -1042,7 +1030,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sito ha pagine dedicate a 'Bologna' per aspirazione/abbattimento polveri/fumi/rumore - copertura commerciale in ER confermata, ma sede legale in Veneto.</t>
+          <t>Sito ha pagine dedicate a 'Bologna' per aspirazione/abbattimento polveri/fumi/rumore - copertura commerciale in ER confermata, ma sede legale in Veneto. [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1072,11 +1060,9 @@
           <t>Impianti aspirazione gas di scarico, polveri, fumi di saldatura per settore automotive/riparazione veicoli</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Marchio di AGM Forniture Industriali Srl, sede legale verificata (visure) a Pianezze, Vicenza. Azienda reale (~9,6 mln EUR fatturato 2024, 37 dipendenti) ma fuori regione target.</t>
+          <t>Marchio di AGM Forniture Industriali Srl, sede legale verificata (visure) a Pianezze, Vicenza. Azienda reale (~9,6 mln EUR fatturato 2024, 37 dipendenti) ma fuori regione target. [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
